--- a/project_mark_task/inputs/workflow_catalog.xlsx
+++ b/project_mark_task/inputs/workflow_catalog.xlsx
@@ -577,7 +577,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Internal | Client onboarding</t>
+          <t>Internal | Client onboarding - EU</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -697,7 +697,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Internal | Support ticket triage</t>
+          <t>Internal | Support ticket triage - EU</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -757,7 +757,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Internal | Lead intake to CRM</t>
+          <t>Internal | Lead intake to CRM - EU</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Internal | Document e-sign</t>
+          <t>Internal | Document e-sign - EU</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Tidewater Marine Supply | Document e-sign</t>
+          <t>Tidewater Marine Supply | Document e-sign - EU</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2257,7 +2257,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Quarry Street Cycles | Document e-sign</t>
+          <t>Quarry Street Cycles | Document e-sign - EU</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Eastgate Motors | Booking confirmation</t>
+          <t>Eastgate Motors | Booking confirmation - EU</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2677,7 +2677,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Birchwood Schools Trust | Order sync</t>
+          <t>Birchwood Schools Trust | Order sync - EU</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2707,7 +2707,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Alder Point Accounting | Client onboarding</t>
+          <t>Alder Point Accounting | Client onboarding - EU</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2857,7 +2857,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Brightpath Dental | Invoice reminder</t>
+          <t>Brightpath Dental | Invoice reminder - EU</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -2947,7 +2947,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Quarry Street Cycles | Document e-sign</t>
+          <t>Quarry Street Cycles | Document e-sign - Phase 2</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -2977,7 +2977,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Zephyr Travel Group | Inventory alert</t>
+          <t>Zephyr Travel Group | Inventory alert - EU</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3007,7 +3007,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Alder Point Accounting | Client onboarding</t>
+          <t>Alder Point Accounting | Client onboarding - Phase 2</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3157,7 +3157,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Alder Point Accounting | Inventory alert</t>
+          <t>Alder Point Accounting | Inventory alert - EU</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3277,7 +3277,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Vantage Freight Co | Invoice reminder</t>
+          <t>Vantage Freight Co | Invoice reminder - EU</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3307,7 +3307,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Fernhill Garden Centre | Invoice reminder</t>
+          <t>Fernhill Garden Centre | Invoice reminder - EU</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3547,7 +3547,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Yarrow Health Foods | Booking confirmation</t>
+          <t>Yarrow Health Foods | Booking confirmation - EU</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -3577,7 +3577,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Vantage Freight Co | Invoice reminder</t>
+          <t>Vantage Freight Co | Invoice reminder - Phase 2</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -3667,7 +3667,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Quarry Street Cycles | Weekly KPI report</t>
+          <t>Quarry Street Cycles | Weekly KPI report - EU</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -3817,7 +3817,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Granite Peak Mortgage | Review request</t>
+          <t>Granite Peak Mortgage | Review request - EU</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -3997,7 +3997,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Pinecrest Physio | Weekly KPI report</t>
+          <t>Pinecrest Physio | Weekly KPI report - EU</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -4027,7 +4027,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Hollis &amp; Reed Architects | Review request</t>
+          <t>Hollis &amp; Reed Architects | Review request - EU</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">

--- a/project_mark_task/inputs/workflow_catalog.xlsx
+++ b/project_mark_task/inputs/workflow_catalog.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F121"/>
+  <dimension ref="A1:G121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,6 +448,11 @@
           <t>required_connectors</t>
         </is>
       </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -478,6 +483,7 @@
           <t>calendar_booking;chat_ops;ecom_orders</t>
         </is>
       </c>
+      <c r="G2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -508,6 +514,7 @@
           <t>sms_gateway</t>
         </is>
       </c>
+      <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -538,6 +545,7 @@
           <t>ecom_orders;chat_ops</t>
         </is>
       </c>
+      <c r="G4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -568,6 +576,11 @@
           <t>sms_gateway;calendar_booking</t>
         </is>
       </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>owner: MK</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -598,6 +611,7 @@
           <t>sheet_store;ecom_orders</t>
         </is>
       </c>
+      <c r="G6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -628,6 +642,7 @@
           <t>esign;forms</t>
         </is>
       </c>
+      <c r="G7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -658,6 +673,7 @@
           <t>ledger_sync</t>
         </is>
       </c>
+      <c r="G8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -688,6 +704,11 @@
           <t>sheet_store</t>
         </is>
       </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>reviewed with client in June</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -718,6 +739,7 @@
           <t>warehouse_api;sheet_store</t>
         </is>
       </c>
+      <c r="G10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -748,6 +770,7 @@
           <t>esign;ledger_sync</t>
         </is>
       </c>
+      <c r="G11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -778,6 +801,7 @@
           <t>forms;crm_core;ledger_sync</t>
         </is>
       </c>
+      <c r="G12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -808,6 +832,7 @@
           <t>helpdesk;sms_gateway</t>
         </is>
       </c>
+      <c r="G13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -838,6 +863,7 @@
           <t>calendar_booking;ecom_orders;forms</t>
         </is>
       </c>
+      <c r="G14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -868,6 +894,7 @@
           <t>warehouse_api;calendar_booking;helpdesk</t>
         </is>
       </c>
+      <c r="G15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -898,6 +925,7 @@
           <t>chat_ops;calendar_booking;ai_extract</t>
         </is>
       </c>
+      <c r="G16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -928,6 +956,11 @@
           <t>warehouse_api;ledger_sync</t>
         </is>
       </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>called from W110 (one call per run)</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -958,6 +991,7 @@
           <t>forms;helpdesk</t>
         </is>
       </c>
+      <c r="G18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -988,6 +1022,7 @@
           <t>ai_extract</t>
         </is>
       </c>
+      <c r="G19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1018,6 +1053,7 @@
           <t>warehouse_api;ledger_sync;esign</t>
         </is>
       </c>
+      <c r="G20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1048,6 +1084,7 @@
           <t>esign</t>
         </is>
       </c>
+      <c r="G21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1078,6 +1115,7 @@
           <t>forms;crm_core</t>
         </is>
       </c>
+      <c r="G22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1108,6 +1146,7 @@
           <t>chat_ops</t>
         </is>
       </c>
+      <c r="G23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1138,6 +1177,7 @@
           <t>sheet_store;ecom_orders;forms</t>
         </is>
       </c>
+      <c r="G24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1168,6 +1208,11 @@
           <t>ecom_orders;helpdesk</t>
         </is>
       </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>sub-flow, called by W095 via webhook for every run</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1198,6 +1243,11 @@
           <t>sms_gateway;ledger_sync</t>
         </is>
       </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>client asked for weekday-only handling</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1228,6 +1278,7 @@
           <t>ledger_sync;chat_ops</t>
         </is>
       </c>
+      <c r="G27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1258,6 +1309,7 @@
           <t>ai_extract;calendar_booking</t>
         </is>
       </c>
+      <c r="G28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1288,6 +1340,7 @@
           <t>ledger_sync</t>
         </is>
       </c>
+      <c r="G29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1318,6 +1371,11 @@
           <t>ecom_orders;calendar_booking</t>
         </is>
       </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>owner: MK</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1348,6 +1406,7 @@
           <t>ai_extract;calendar_booking;esign</t>
         </is>
       </c>
+      <c r="G31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1378,6 +1437,7 @@
           <t>esign</t>
         </is>
       </c>
+      <c r="G32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1408,6 +1468,7 @@
           <t>crm_core;ai_extract;warehouse_api</t>
         </is>
       </c>
+      <c r="G33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1438,6 +1499,7 @@
           <t>helpdesk;sheet_store</t>
         </is>
       </c>
+      <c r="G34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1468,6 +1530,7 @@
           <t>ledger_sync</t>
         </is>
       </c>
+      <c r="G35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1498,6 +1561,11 @@
           <t>sms_gateway</t>
         </is>
       </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>owner: MK</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1528,6 +1596,7 @@
           <t>ledger_sync</t>
         </is>
       </c>
+      <c r="G37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1558,6 +1627,7 @@
           <t>chat_ops</t>
         </is>
       </c>
+      <c r="G38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1588,6 +1658,7 @@
           <t>ecom_orders;helpdesk</t>
         </is>
       </c>
+      <c r="G39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1618,6 +1689,11 @@
           <t>ecom_orders;chat_ops;warehouse_api</t>
         </is>
       </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>helper scenario invoked by W044; no trigger of its own</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1648,6 +1724,7 @@
           <t>warehouse_api</t>
         </is>
       </c>
+      <c r="G41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1678,6 +1755,7 @@
           <t>helpdesk;ledger_sync</t>
         </is>
       </c>
+      <c r="G42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1708,6 +1786,7 @@
           <t>chat_ops;sms_gateway</t>
         </is>
       </c>
+      <c r="G43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1738,6 +1817,7 @@
           <t>sms_gateway</t>
         </is>
       </c>
+      <c r="G44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1768,6 +1848,11 @@
           <t>forms</t>
         </is>
       </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>pilot for the Q2 upsell</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1798,6 +1883,7 @@
           <t>ledger_sync</t>
         </is>
       </c>
+      <c r="G46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1828,6 +1914,7 @@
           <t>sheet_store</t>
         </is>
       </c>
+      <c r="G47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1858,6 +1945,11 @@
           <t>sms_gateway;warehouse_api;helpdesk</t>
         </is>
       </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>called from W096 (one call per run)</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1888,6 +1980,7 @@
           <t>warehouse_api</t>
         </is>
       </c>
+      <c r="G49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1918,6 +2011,7 @@
           <t>calendar_booking;chat_ops;ecom_orders</t>
         </is>
       </c>
+      <c r="G50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1948,6 +2042,7 @@
           <t>ecom_orders;helpdesk</t>
         </is>
       </c>
+      <c r="G51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1978,6 +2073,7 @@
           <t>forms;ecom_orders</t>
         </is>
       </c>
+      <c r="G52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2008,6 +2104,7 @@
           <t>sms_gateway</t>
         </is>
       </c>
+      <c r="G53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2038,6 +2135,7 @@
           <t>crm_core;helpdesk</t>
         </is>
       </c>
+      <c r="G54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2068,6 +2166,7 @@
           <t>forms</t>
         </is>
       </c>
+      <c r="G55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2098,6 +2197,7 @@
           <t>crm_core</t>
         </is>
       </c>
+      <c r="G56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2128,6 +2228,7 @@
           <t>warehouse_api</t>
         </is>
       </c>
+      <c r="G57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2158,6 +2259,7 @@
           <t>ecom_orders;warehouse_api;esign</t>
         </is>
       </c>
+      <c r="G58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2188,6 +2290,11 @@
           <t>helpdesk;forms</t>
         </is>
       </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>helper scenario invoked by W087; no trigger of its own</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2218,6 +2325,7 @@
           <t>sms_gateway;crm_core</t>
         </is>
       </c>
+      <c r="G60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2248,6 +2356,7 @@
           <t>ecom_orders;sms_gateway</t>
         </is>
       </c>
+      <c r="G61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2278,6 +2387,7 @@
           <t>crm_core</t>
         </is>
       </c>
+      <c r="G62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2308,6 +2418,7 @@
           <t>helpdesk</t>
         </is>
       </c>
+      <c r="G63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2338,6 +2449,7 @@
           <t>warehouse_api;calendar_booking</t>
         </is>
       </c>
+      <c r="G64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2368,6 +2480,7 @@
           <t>warehouse_api</t>
         </is>
       </c>
+      <c r="G65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2398,6 +2511,7 @@
           <t>ecom_orders</t>
         </is>
       </c>
+      <c r="G66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2428,6 +2542,7 @@
           <t>chat_ops</t>
         </is>
       </c>
+      <c r="G67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2458,6 +2573,7 @@
           <t>chat_ops</t>
         </is>
       </c>
+      <c r="G68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2488,6 +2604,7 @@
           <t>ai_extract</t>
         </is>
       </c>
+      <c r="G69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2518,6 +2635,11 @@
           <t>forms;crm_core</t>
         </is>
       </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>called from W119 (one call per run)</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2548,6 +2670,7 @@
           <t>calendar_booking;ledger_sync</t>
         </is>
       </c>
+      <c r="G71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2578,6 +2701,7 @@
           <t>forms;chat_ops</t>
         </is>
       </c>
+      <c r="G72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2608,6 +2732,7 @@
           <t>forms;ecom_orders;calendar_booking</t>
         </is>
       </c>
+      <c r="G73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2638,6 +2763,7 @@
           <t>crm_core;esign;warehouse_api</t>
         </is>
       </c>
+      <c r="G74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2668,6 +2794,7 @@
           <t>calendar_booking;ai_extract</t>
         </is>
       </c>
+      <c r="G75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2698,6 +2825,7 @@
           <t>ledger_sync</t>
         </is>
       </c>
+      <c r="G76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -2728,6 +2856,7 @@
           <t>sheet_store</t>
         </is>
       </c>
+      <c r="G77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2758,6 +2887,7 @@
           <t>sms_gateway;chat_ops</t>
         </is>
       </c>
+      <c r="G78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -2788,6 +2918,11 @@
           <t>forms;ledger_sync</t>
         </is>
       </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>called from W057 (one call per run)</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -2818,6 +2953,7 @@
           <t>esign;calendar_booking;warehouse_api</t>
         </is>
       </c>
+      <c r="G80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -2848,6 +2984,7 @@
           <t>crm_core;sheet_store</t>
         </is>
       </c>
+      <c r="G81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -2878,6 +3015,11 @@
           <t>warehouse_api</t>
         </is>
       </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>paused over the August holiday</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -2908,6 +3050,11 @@
           <t>helpdesk</t>
         </is>
       </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>helper scenario invoked by W089; no trigger of its own</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -2938,6 +3085,7 @@
           <t>ecom_orders</t>
         </is>
       </c>
+      <c r="G84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -2968,6 +3116,7 @@
           <t>calendar_booking;forms;warehouse_api</t>
         </is>
       </c>
+      <c r="G85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -2998,6 +3147,7 @@
           <t>calendar_booking;helpdesk</t>
         </is>
       </c>
+      <c r="G86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -3028,6 +3178,7 @@
           <t>ai_extract</t>
         </is>
       </c>
+      <c r="G87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -3058,6 +3209,7 @@
           <t>ecom_orders;calendar_booking;helpdesk</t>
         </is>
       </c>
+      <c r="G88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -3088,6 +3240,7 @@
           <t>sheet_store;ecom_orders</t>
         </is>
       </c>
+      <c r="G89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -3118,6 +3271,7 @@
           <t>forms;esign</t>
         </is>
       </c>
+      <c r="G90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -3148,6 +3302,7 @@
           <t>sms_gateway</t>
         </is>
       </c>
+      <c r="G91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -3178,6 +3333,7 @@
           <t>sms_gateway</t>
         </is>
       </c>
+      <c r="G92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -3208,6 +3364,11 @@
           <t>esign;sheet_store;ai_extract</t>
         </is>
       </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>owner: JL</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -3238,6 +3399,7 @@
           <t>crm_core</t>
         </is>
       </c>
+      <c r="G94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -3268,6 +3430,11 @@
           <t>helpdesk;warehouse_api;sheet_store</t>
         </is>
       </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>reviewed with client in June</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -3298,6 +3465,11 @@
           <t>sms_gateway;ai_extract</t>
         </is>
       </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>client asked for weekday-only handling</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -3328,6 +3500,7 @@
           <t>esign;chat_ops;sheet_store</t>
         </is>
       </c>
+      <c r="G97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -3358,6 +3531,7 @@
           <t>ecom_orders;ledger_sync</t>
         </is>
       </c>
+      <c r="G98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -3388,6 +3562,7 @@
           <t>chat_ops;sms_gateway;ai_extract</t>
         </is>
       </c>
+      <c r="G99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -3418,6 +3593,7 @@
           <t>sheet_store</t>
         </is>
       </c>
+      <c r="G100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -3448,6 +3624,7 @@
           <t>sheet_store;crm_core;chat_ops</t>
         </is>
       </c>
+      <c r="G101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -3478,6 +3655,7 @@
           <t>ledger_sync</t>
         </is>
       </c>
+      <c r="G102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -3508,6 +3686,11 @@
           <t>crm_core;calendar_booking</t>
         </is>
       </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>client asked for weekday-only handling</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -3538,6 +3721,7 @@
           <t>calendar_booking;helpdesk;ai_extract</t>
         </is>
       </c>
+      <c r="G104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -3568,6 +3752,11 @@
           <t>forms;helpdesk</t>
         </is>
       </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>called from W068 (one call per run)</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -3598,6 +3787,11 @@
           <t>helpdesk</t>
         </is>
       </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>reviewed with client in June</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -3628,6 +3822,11 @@
           <t>ledger_sync;calendar_booking</t>
         </is>
       </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>sub-flow, called by W040 via webhook for every run</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -3658,6 +3857,7 @@
           <t>ecom_orders;ledger_sync</t>
         </is>
       </c>
+      <c r="G108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -3688,6 +3888,7 @@
           <t>helpdesk;esign;ecom_orders</t>
         </is>
       </c>
+      <c r="G109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -3718,6 +3919,7 @@
           <t>chat_ops</t>
         </is>
       </c>
+      <c r="G110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -3748,6 +3950,11 @@
           <t>chat_ops</t>
         </is>
       </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>owner: MK</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -3778,6 +3985,7 @@
           <t>crm_core;sheet_store</t>
         </is>
       </c>
+      <c r="G112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -3808,6 +4016,11 @@
           <t>helpdesk;ledger_sync;sheet_store</t>
         </is>
       </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>sub-flow, called by W015 via webhook for every run</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -3838,6 +4051,7 @@
           <t>forms;sms_gateway</t>
         </is>
       </c>
+      <c r="G114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -3868,6 +4082,7 @@
           <t>warehouse_api;forms;ai_extract</t>
         </is>
       </c>
+      <c r="G115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -3898,6 +4113,7 @@
           <t>warehouse_api;esign;helpdesk</t>
         </is>
       </c>
+      <c r="G116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -3928,6 +4144,7 @@
           <t>sms_gateway;warehouse_api</t>
         </is>
       </c>
+      <c r="G117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -3958,6 +4175,7 @@
           <t>chat_ops;calendar_booking</t>
         </is>
       </c>
+      <c r="G118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -3988,6 +4206,7 @@
           <t>warehouse_api;esign</t>
         </is>
       </c>
+      <c r="G119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -4018,6 +4237,7 @@
           <t>ledger_sync;ecom_orders</t>
         </is>
       </c>
+      <c r="G120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -4048,6 +4268,7 @@
           <t>sheet_store;ai_extract</t>
         </is>
       </c>
+      <c r="G121" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/project_mark_task/inputs/workflow_catalog.xlsx
+++ b/project_mark_task/inputs/workflow_catalog.xlsx
@@ -576,11 +576,7 @@
           <t>sms_gateway;calendar_booking</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>owner: MK</t>
-        </is>
-      </c>
+      <c r="G5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -642,7 +638,11 @@
           <t>esign;forms</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>owner: MK</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -704,11 +704,7 @@
           <t>sheet_store</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>reviewed with client in June</t>
-        </is>
-      </c>
+      <c r="G9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -739,7 +735,11 @@
           <t>warehouse_api;sheet_store</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>reviewed with client in June</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1084,7 +1084,11 @@
           <t>esign</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>owner: JL</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1210,7 +1214,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>sub-flow, called by W095 via webhook for every run</t>
+          <t>called from W095 (one call per run)</t>
         </is>
       </c>
     </row>
@@ -1243,11 +1247,7 @@
           <t>sms_gateway;ledger_sync</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>client asked for weekday-only handling</t>
-        </is>
-      </c>
+      <c r="G26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1340,7 +1340,11 @@
           <t>ledger_sync</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>paused over the August holiday</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1373,7 +1377,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>owner: MK</t>
+          <t>uses client's own API key</t>
         </is>
       </c>
     </row>
@@ -1468,7 +1472,11 @@
           <t>crm_core;ai_extract;warehouse_api</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>pilot for the Q2 upsell</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1499,7 +1507,11 @@
           <t>helpdesk;sheet_store</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>pilot for the Q2 upsell</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1530,7 +1542,11 @@
           <t>ledger_sync</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>pilot for the Q2 upsell</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1561,11 +1577,7 @@
           <t>sms_gateway</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>owner: MK</t>
-        </is>
-      </c>
+      <c r="G36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1596,7 +1608,11 @@
           <t>ledger_sync</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>paused over the August holiday</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1627,7 +1643,11 @@
           <t>chat_ops</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>owner: MK</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1786,7 +1806,11 @@
           <t>chat_ops;sms_gateway</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>paused over the August holiday</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1848,11 +1872,7 @@
           <t>forms</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>pilot for the Q2 upsell</t>
-        </is>
-      </c>
+      <c r="G45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1947,7 +1967,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>called from W096 (one call per run)</t>
+          <t>helper scenario invoked by W096; no trigger of its own</t>
         </is>
       </c>
     </row>
@@ -2701,7 +2721,11 @@
           <t>forms;chat_ops</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr"/>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>client asked for weekday-only handling</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2732,7 +2756,11 @@
           <t>forms;ecom_orders;calendar_booking</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr"/>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>owner: MK</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2887,7 +2915,11 @@
           <t>sms_gateway;chat_ops</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr"/>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>client asked for weekday-only handling</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -2920,7 +2952,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>called from W057 (one call per run)</t>
+          <t>helper scenario invoked by W057; no trigger of its own</t>
         </is>
       </c>
     </row>
@@ -2953,7 +2985,11 @@
           <t>esign;calendar_booking;warehouse_api</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr"/>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>client asked for weekday-only handling</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -2984,7 +3020,11 @@
           <t>crm_core;sheet_store</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr"/>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>uses client's own API key</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -3015,11 +3055,7 @@
           <t>warehouse_api</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>paused over the August holiday</t>
-        </is>
-      </c>
+      <c r="G82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -3178,7 +3214,11 @@
           <t>ai_extract</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr"/>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>paused over the August holiday</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -3366,7 +3406,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>owner: JL</t>
+          <t>pilot for the Q2 upsell</t>
         </is>
       </c>
     </row>
@@ -3430,11 +3470,7 @@
           <t>helpdesk;warehouse_api;sheet_store</t>
         </is>
       </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>reviewed with client in June</t>
-        </is>
-      </c>
+      <c r="G95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -3465,11 +3501,7 @@
           <t>sms_gateway;ai_extract</t>
         </is>
       </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>client asked for weekday-only handling</t>
-        </is>
-      </c>
+      <c r="G96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -3624,7 +3656,11 @@
           <t>sheet_store;crm_core;chat_ops</t>
         </is>
       </c>
-      <c r="G101" t="inlineStr"/>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>client asked for weekday-only handling</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -3686,11 +3722,7 @@
           <t>crm_core;calendar_booking</t>
         </is>
       </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>client asked for weekday-only handling</t>
-        </is>
-      </c>
+      <c r="G103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -3787,11 +3819,7 @@
           <t>helpdesk</t>
         </is>
       </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>reviewed with client in June</t>
-        </is>
-      </c>
+      <c r="G106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -3950,11 +3978,7 @@
           <t>chat_ops</t>
         </is>
       </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>owner: MK</t>
-        </is>
-      </c>
+      <c r="G111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -4018,7 +4042,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>sub-flow, called by W015 via webhook for every run</t>
+          <t>called from W015 (one call per run)</t>
         </is>
       </c>
     </row>
@@ -4113,7 +4137,11 @@
           <t>warehouse_api;esign;helpdesk</t>
         </is>
       </c>
-      <c r="G116" t="inlineStr"/>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>owner: MK</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -4175,7 +4203,11 @@
           <t>chat_ops;calendar_booking</t>
         </is>
       </c>
-      <c r="G118" t="inlineStr"/>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>triggered by account manager from the CRM button</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -4206,7 +4238,11 @@
           <t>warehouse_api;esign</t>
         </is>
       </c>
-      <c r="G119" t="inlineStr"/>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>client asked for weekday-only handling</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">

--- a/project_mark_task/inputs/workflow_catalog.xlsx
+++ b/project_mark_task/inputs/workflow_catalog.xlsx
@@ -638,11 +638,7 @@
           <t>esign;forms</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>owner: MK</t>
-        </is>
-      </c>
+      <c r="G7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -704,7 +700,11 @@
           <t>sheet_store</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>owner: JL</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -735,11 +735,7 @@
           <t>warehouse_api;sheet_store</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>reviewed with client in June</t>
-        </is>
-      </c>
+      <c r="G10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -958,7 +954,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>called from W110 (one call per run)</t>
+          <t>helper scenario invoked by W110; no trigger of its own</t>
         </is>
       </c>
     </row>
@@ -1084,11 +1080,7 @@
           <t>esign</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>owner: JL</t>
-        </is>
-      </c>
+      <c r="G21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1119,7 +1111,11 @@
           <t>forms;crm_core</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>uses client's own API key</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1212,11 +1208,7 @@
           <t>ecom_orders;helpdesk</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>called from W095 (one call per run)</t>
-        </is>
-      </c>
+      <c r="G25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1247,7 +1239,11 @@
           <t>sms_gateway;ledger_sync</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>helper scenario invoked by W097; no trigger of its own</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1340,11 +1336,7 @@
           <t>ledger_sync</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>paused over the August holiday</t>
-        </is>
-      </c>
+      <c r="G29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1375,11 +1367,7 @@
           <t>ecom_orders;calendar_booking</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>uses client's own API key</t>
-        </is>
-      </c>
+      <c r="G30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1472,11 +1460,7 @@
           <t>crm_core;ai_extract;warehouse_api</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>pilot for the Q2 upsell</t>
-        </is>
-      </c>
+      <c r="G33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1507,11 +1491,7 @@
           <t>helpdesk;sheet_store</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>pilot for the Q2 upsell</t>
-        </is>
-      </c>
+      <c r="G34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1542,11 +1522,7 @@
           <t>ledger_sync</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>pilot for the Q2 upsell</t>
-        </is>
-      </c>
+      <c r="G35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1610,7 +1586,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>paused over the August holiday</t>
+          <t>uses client's own API key</t>
         </is>
       </c>
     </row>
@@ -1643,11 +1619,7 @@
           <t>chat_ops</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>owner: MK</t>
-        </is>
-      </c>
+      <c r="G38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1711,7 +1683,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>helper scenario invoked by W044; no trigger of its own</t>
+          <t>called from W059 (one call per run)</t>
         </is>
       </c>
     </row>
@@ -1806,11 +1778,7 @@
           <t>chat_ops;sms_gateway</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>paused over the August holiday</t>
-        </is>
-      </c>
+      <c r="G43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1967,7 +1935,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>helper scenario invoked by W096; no trigger of its own</t>
+          <t>client asked for weekday-only handling</t>
         </is>
       </c>
     </row>
@@ -2000,7 +1968,11 @@
           <t>warehouse_api</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>helper scenario invoked by W096; no trigger of its own</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2217,7 +2189,11 @@
           <t>crm_core</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr"/>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>pilot for the Q2 upsell</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2248,7 +2224,11 @@
           <t>warehouse_api</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr"/>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>uses client's own API key</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2310,11 +2290,7 @@
           <t>helpdesk;forms</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>helper scenario invoked by W087; no trigger of its own</t>
-        </is>
-      </c>
+      <c r="G59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2376,7 +2352,11 @@
           <t>ecom_orders;sms_gateway</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr"/>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>called from W118 (one call per run)</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2593,7 +2573,11 @@
           <t>chat_ops</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr"/>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>uses client's own API key</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2655,11 +2639,7 @@
           <t>forms;crm_core</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>called from W119 (one call per run)</t>
-        </is>
-      </c>
+      <c r="G70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2723,7 +2703,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>client asked for weekday-only handling</t>
+          <t>sub-flow, called by W044 via webhook for every run</t>
         </is>
       </c>
     </row>
@@ -2756,11 +2736,7 @@
           <t>forms;ecom_orders;calendar_booking</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>owner: MK</t>
-        </is>
-      </c>
+      <c r="G73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2917,7 +2893,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>client asked for weekday-only handling</t>
+          <t>owner: JL</t>
         </is>
       </c>
     </row>
@@ -2952,7 +2928,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>helper scenario invoked by W057; no trigger of its own</t>
+          <t>owner: MK</t>
         </is>
       </c>
     </row>
@@ -2987,7 +2963,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>client asked for weekday-only handling</t>
+          <t>sub-flow, called by W014 via webhook for every run</t>
         </is>
       </c>
     </row>
@@ -3020,11 +2996,7 @@
           <t>crm_core;sheet_store</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>uses client's own API key</t>
-        </is>
-      </c>
+      <c r="G81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -3086,11 +3058,7 @@
           <t>helpdesk</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>helper scenario invoked by W089; no trigger of its own</t>
-        </is>
-      </c>
+      <c r="G83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -3121,7 +3089,11 @@
           <t>ecom_orders</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr"/>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>called from W095 (one call per run)</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -3214,11 +3186,7 @@
           <t>ai_extract</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>paused over the August holiday</t>
-        </is>
-      </c>
+      <c r="G87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -3373,7 +3341,11 @@
           <t>sms_gateway</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr"/>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>client asked for weekday-only handling</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -3404,11 +3376,7 @@
           <t>esign;sheet_store;ai_extract</t>
         </is>
       </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>pilot for the Q2 upsell</t>
-        </is>
-      </c>
+      <c r="G93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -3594,7 +3562,11 @@
           <t>chat_ops;sms_gateway;ai_extract</t>
         </is>
       </c>
-      <c r="G99" t="inlineStr"/>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>paused over the August holiday</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -3656,11 +3628,7 @@
           <t>sheet_store;crm_core;chat_ops</t>
         </is>
       </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>client asked for weekday-only handling</t>
-        </is>
-      </c>
+      <c r="G101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -3753,7 +3721,11 @@
           <t>calendar_booking;helpdesk;ai_extract</t>
         </is>
       </c>
-      <c r="G104" t="inlineStr"/>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>sub-flow, called by W037 via webhook for every run</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -3784,11 +3756,7 @@
           <t>forms;helpdesk</t>
         </is>
       </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>called from W068 (one call per run)</t>
-        </is>
-      </c>
+      <c r="G105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -3852,7 +3820,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>sub-flow, called by W040 via webhook for every run</t>
+          <t>called from W040 (one call per run)</t>
         </is>
       </c>
     </row>
@@ -4042,7 +4010,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>called from W015 (one call per run)</t>
+          <t>helper scenario invoked by W015; no trigger of its own</t>
         </is>
       </c>
     </row>
@@ -4137,11 +4105,7 @@
           <t>warehouse_api;esign;helpdesk</t>
         </is>
       </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>owner: MK</t>
-        </is>
-      </c>
+      <c r="G116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -4172,7 +4136,11 @@
           <t>sms_gateway;warehouse_api</t>
         </is>
       </c>
-      <c r="G117" t="inlineStr"/>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>paused over the August holiday</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -4203,11 +4171,7 @@
           <t>chat_ops;calendar_booking</t>
         </is>
       </c>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>triggered by account manager from the CRM button</t>
-        </is>
-      </c>
+      <c r="G118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -4238,11 +4202,7 @@
           <t>warehouse_api;esign</t>
         </is>
       </c>
-      <c r="G119" t="inlineStr">
-        <is>
-          <t>client asked for weekday-only handling</t>
-        </is>
-      </c>
+      <c r="G119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
